--- a/accountant-skill/data/output/Jan2026/financial_statements_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/financial_statements_Jan2026.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,7 +66,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF0000"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
       <sz val="11"/>
     </font>
     <font>
@@ -81,12 +83,23 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +114,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -157,10 +175,10 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,8 +189,14 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -659,10 +683,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.0701</v>
+        <v>0.0615</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
     </row>
@@ -673,7 +697,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>12160750</v>
+        <v>13215750</v>
       </c>
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -697,7 +721,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>9207750</v>
+        <v>9142750</v>
       </c>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
@@ -739,12 +763,12 @@
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
-      <c r="C18" s="9" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -756,7 +780,7 @@
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
@@ -803,7 +827,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -835,7 +859,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
@@ -861,22 +885,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Balance Sheet does NOT balance: Assets=12,160,750.00, Equity+Liab=13,280,750.00, Diff=-1,120,000.00</t>
+          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(462,750.00) != Closing(0.00), Diff=462,750.00</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(527,750.00) != Closing(0.00), Diff=527,750.00</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr"/>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -899,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1104,80 +1118,80 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Opening Inventory - Raw Materials</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>-2096000</v>
+          <t>Purchases Packaging</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>-225000</v>
       </c>
       <c r="D24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>50100</t>
+          <t>50320</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Opening Inventory - Packaging</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>-225000</v>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>-2096000</v>
       </c>
       <c r="D25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>50310</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Closing Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>65000</v>
+          <t>Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>-2755000</v>
       </c>
       <c r="D26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>-120000</v>
+          <t>Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>-95000</v>
       </c>
       <c r="D27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>-2755000</v>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>-120000</v>
       </c>
       <c r="D28" s="7" t="n"/>
     </row>
@@ -1192,7 +1206,7 @@
           <t>Meal Allowance Expense</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="15" t="n">
         <v>-120000</v>
       </c>
       <c r="D29" s="7" t="n"/>
@@ -1208,7 +1222,7 @@
           <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="15" t="n">
         <v>-125000</v>
       </c>
       <c r="D30" s="7" t="n"/>
@@ -1224,7 +1238,7 @@
           <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="15" t="n">
         <v>-85000</v>
       </c>
       <c r="D31" s="7" t="n"/>
@@ -1240,8 +1254,8 @@
           <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
-        <v>-1486500</v>
+      <c r="C32" s="15" t="n">
+        <v>-63000</v>
       </c>
       <c r="D32" s="7" t="n"/>
     </row>
@@ -1256,59 +1270,75 @@
           <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="15" t="n">
         <v>-54750</v>
       </c>
       <c r="D33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>68000</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>-1328500</v>
+      </c>
+      <c r="D34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>NET OTHER INCOME/(EXPENSES)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="15" t="n">
-        <v>-7002250</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="16" t="n">
+        <v>-7067250</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>PROFIT BEFORE TAX</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n">
-        <v>527750</v>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n">
+        <v>462750</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>NET PROFIT / (LOSS)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n">
-        <v>527750</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n">
+        <v>462750</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Net Profit Margin</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="8" t="n">
-        <v>0.0701</v>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="8" t="n">
+        <v>0.0615</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1488,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -1481,196 +1511,196 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Inventory - Finished Goods</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>260000</v>
+          <t xml:space="preserve">  Inventory Adjustments</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>-15000</v>
       </c>
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Work-in-Progress</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>65000</v>
+        <v>100000</v>
       </c>
       <c r="D15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="D16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>5000000</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>-518750</v>
       </c>
       <c r="D17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated Depreciation - Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-518750</v>
+          <t>Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3000000</v>
       </c>
       <c r="D18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>3000000</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>-472500</v>
       </c>
       <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>-472500</v>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>800000</v>
       </c>
       <c r="D20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>500000</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>-166000</v>
       </c>
       <c r="D21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated Depreciation - Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>-113500</v>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>500000</v>
       </c>
       <c r="D22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Depreciation - Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>-107500</v>
+      </c>
+      <c r="D23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>TOTAL CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n">
-        <v>12160750</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n">
+        <v>13215750</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n">
-        <v>12160750</v>
-      </c>
-    </row>
-    <row r="26"/>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n">
+        <v>13215750</v>
+      </c>
+    </row>
     <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>30200</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Account 30200</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>-200000</v>
-      </c>
-      <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1684,7 +1714,7 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
       <c r="D30" s="7" t="n"/>
     </row>
@@ -1716,7 +1746,7 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="D32" s="7" t="n"/>
     </row>
@@ -1729,7 +1759,7 @@
       <c r="B33" s="12" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="12" t="n">
-        <v>9207750</v>
+        <v>9142750</v>
       </c>
     </row>
     <row r="34"/>
@@ -1866,7 +1896,7 @@
       <c r="B47" s="14" t="n"/>
       <c r="C47" s="14" t="n"/>
       <c r="D47" s="14" t="n">
-        <v>13280750</v>
+        <v>13215750</v>
       </c>
     </row>
     <row r="48"/>
@@ -1877,12 +1907,12 @@
           <t>CHECK: Assets - (Equity + Liabilities)</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1924,1087 @@
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Breakdown of Financial Statement Accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>As at 2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1. ASSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Account Receivable</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Total Account Receivable</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>3360000</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Total Advanced Payments</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash in hand</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash at Bank</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1435500</v>
+      </c>
+      <c r="D17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n">
+        <v>1585500</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory - Raw Material</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>12300</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory Adjustments</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Total Inventory</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>15100</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>15110</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>518750</v>
+      </c>
+      <c r="D27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>472500</v>
+      </c>
+      <c r="D29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>15300</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="D30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>15310</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>166000</v>
+      </c>
+      <c r="D31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>15400</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Depreciation - Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>107500</v>
+      </c>
+      <c r="D33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Total Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n">
+        <v>10564750</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL ASSET</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n">
+        <v>15775250</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2. LIABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Account Payables</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="D41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Total Account Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n">
+        <v>1368000</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Accured Expenses</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wages Payable</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>205000</v>
+      </c>
+      <c r="D45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Total Accured Expenses</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bank Loan</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Total Bank Loan</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr"/>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Short-term loans</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Short-term Loans</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>Total Short-term loans</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITY</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n">
+        <v>4073000</v>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3. EQUITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>31000</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Paid-up Capital</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>7480000</v>
+      </c>
+      <c r="D61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n">
+        <v>7480000</v>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>32000</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Total Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="14" t="n">
+        <v>8680000</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>INCOME STATEMENT NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>4. REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr"/>
+      <c r="D74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest Income</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales Revenue</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>7515000</v>
+      </c>
+      <c r="D79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n">
+        <v>7515000</v>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n"/>
+      <c r="C82" s="14" t="n"/>
+      <c r="D82" s="14" t="n">
+        <v>7530000</v>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>5. EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Cost of Production</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>50110</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchases Packaging</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>50320</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="D88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>Total Cost of Production</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="12" t="n"/>
+      <c r="D89" s="12" t="n">
+        <v>2321000</v>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr"/>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Production Overhead Costs</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>53000</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="D92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>53100</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>Total Production Overhead Costs</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr"/>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>62000</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Meal Allowance Expense</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>63000</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="D99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>64000</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>63000</v>
+      </c>
+      <c r="D101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>66000</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="D102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>68000</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Expenses</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="D103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Total SG&amp;A</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n"/>
+      <c r="C104" s="12" t="n"/>
+      <c r="D104" s="12" t="n">
+        <v>1896250</v>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n"/>
+      <c r="C106" s="14" t="n"/>
+      <c r="D106" s="14" t="n">
+        <v>7067250</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A85:D85"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004472C4"/>
@@ -1980,7 +3083,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="D7" s="7" t="n"/>
     </row>
@@ -1994,7 +3097,7 @@
       <c r="B9" s="12" t="n"/>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="12" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
     </row>
     <row r="10"/>
@@ -2063,7 +3166,7 @@
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="14" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
     </row>
     <row r="20"/>
@@ -2096,7 +3199,7 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>527750</v>
+        <v>462750</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -2117,14 +3220,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FF0000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2170,17 +3273,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Balance Sheet does NOT balance: Assets=12,160,750.00, Equity+Liab=13,280,750.00, Diff=-1,120,000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(527,750.00) != Closing(0.00), Diff=527,750.00</t>
+          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(462,750.00) != Closing(0.00), Diff=462,750.00</t>
         </is>
       </c>
     </row>
